--- a/Simplus-Grid-Tool-fIMR/fIMR_case/IEEE68_GFM_improved.xlsx
+++ b/Simplus-Grid-Tool-fIMR/fIMR_case/IEEE68_GFM_improved.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\徐瑞廷\科研相关\论文撰写\新型阻抗判据研究\Simplus-Grid-Tool-2025（V5，加扫频）\fIMR_case\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\徐瑞廷\科研相关\论文撰写\在校期间的论文和代码\Simplus-Grid-Tool-2025（V6，上传版本）\fIMR_case\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{408B2DFB-C1B8-43D2-AA51-BF0CF13726CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E1D327-A5B0-4C1D-9290-D10A2AA12AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -567,20 +567,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.00_ "/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -589,7 +589,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -597,7 +597,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -605,7 +605,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -613,13 +613,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -640,7 +640,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -659,7 +659,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -672,14 +672,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B050"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -690,7 +690,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -780,13 +780,13 @@
   <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -804,9 +804,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -827,7 +827,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -839,7 +839,7 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="12" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -850,12 +850,12 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1157,11 +1157,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L70"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.265625" customWidth="1"/>
+    <col min="9" max="9" width="10.73046875" customWidth="1"/>
+    <col min="10" max="10" width="11.1328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -3802,12 +3802,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34645F5B-1D7A-4323-9AD6-5FF81941CA24}">
   <dimension ref="A1:AQ81"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" customWidth="1"/>
-    <col min="3" max="43" width="10.7109375" customWidth="1"/>
-    <col min="47" max="47" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.73046875" customWidth="1"/>
+    <col min="2" max="2" width="17.86328125" customWidth="1"/>
+    <col min="3" max="43" width="10.73046875" customWidth="1"/>
+    <col min="47" max="47" width="9.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43">
@@ -5861,13 +5861,13 @@
         <v>0.01</v>
       </c>
       <c r="G39" s="37">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H39" s="37">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I39" s="37">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="J39" s="37">
         <v>15</v>
@@ -5893,13 +5893,13 @@
         <v>0.01</v>
       </c>
       <c r="G40" s="37">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="H40" s="37">
         <v>20</v>
       </c>
       <c r="I40" s="37">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="J40" s="37">
         <v>6</v>
@@ -5925,13 +5925,13 @@
         <v>0.01</v>
       </c>
       <c r="G41" s="37">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H41" s="37">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I41" s="37">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="J41" s="37">
         <v>15</v>
@@ -5957,13 +5957,13 @@
         <v>0.01</v>
       </c>
       <c r="G42" s="37">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H42" s="37">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I42" s="37">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="J42" s="37">
         <v>15</v>
@@ -6201,7 +6201,7 @@
         <v>20</v>
       </c>
       <c r="H56" s="37">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I56" s="37">
         <v>500</v>
@@ -6233,7 +6233,7 @@
         <v>20</v>
       </c>
       <c r="H57" s="37">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I57" s="37">
         <v>500</v>
@@ -6265,7 +6265,7 @@
         <v>20</v>
       </c>
       <c r="H58" s="37">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="I58" s="37">
         <v>500</v>
@@ -6488,7 +6488,7 @@
         <v>20</v>
       </c>
       <c r="I71" s="37">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="J71" s="37">
         <v>6</v>
@@ -6520,7 +6520,7 @@
         <v>20</v>
       </c>
       <c r="I72" s="37">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="J72" s="37">
         <v>6</v>
@@ -6623,12 +6623,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EB93A31-1E5A-4104-8C10-8E6599437516}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.3984375" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.73046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6678,10 +6678,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B0C2B6E-74BD-40FA-8EB6-D64D8C21837A}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" customWidth="1"/>
+    <col min="7" max="7" width="14.86328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6722,10 +6722,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D00B5E-E2E7-41B8-8388-8931D474EA96}">
   <dimension ref="A1:G88"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -8690,9 +8690,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EFCB373-2341-40B6-A375-7BA50357479A}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="30.140625" customWidth="1"/>
+    <col min="1" max="1" width="30.1328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8754,7 +8754,7 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3">
